--- a/appdata/threshold_definitions_res_hist_de.xlsx
+++ b/appdata/threshold_definitions_res_hist_de.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zhaw-my.sharepoint.com/personal/hedd_zhaw_ch/Documents/Dashboard Squarefoot Projekt/Squarefoot/Squarefoot code/squarefoot/appdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:9_{36C0AF89-E858-44E3-B955-074CA1A8DB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD1AE80F-8E93-44E4-8BC3-33841F714327}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:9_{36C0AF89-E858-44E3-B955-074CA1A8DB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28DBFF8C-1957-4618-A298-9717CC37DE5A}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{DF7BF7E8-8078-438A-9C9E-DC555A1DD317}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="11685" windowHeight="15585" firstSheet="2" activeTab="2" xr2:uid="{DF7BF7E8-8078-438A-9C9E-DC555A1DD317}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="2" r:id="rId1"/>
@@ -202,16 +202,16 @@
     <t>funktionale_diversita0et</t>
   </si>
   <si>
-    <t>wenig</t>
+    <t>kleiner</t>
   </si>
   <si>
-    <t>viel</t>
+    <t>klein</t>
   </si>
   <si>
-    <t>noch mehr</t>
+    <t>grösser</t>
   </si>
   <si>
-    <t>noch weniger</t>
+    <t>gross</t>
   </si>
 </sst>
 </file>
@@ -817,10 +817,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -18399,18 +18395,18 @@
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="16" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>58</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>56</v>
       </c>
       <c r="E1" s="16" t="s">
         <v>57</v>
@@ -18421,16 +18417,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>10.06</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>13.9</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>18.346666666000001</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -18438,16 +18434,16 @@
         <v>50</v>
       </c>
       <c r="B3">
-        <v>0.1</v>
+        <v>0.1727265258</v>
       </c>
       <c r="C3">
-        <v>0.2</v>
+        <v>0.21420318699999999</v>
       </c>
       <c r="D3">
-        <v>0.25</v>
+        <v>0.24364943459999999</v>
       </c>
       <c r="E3">
-        <v>0.35</v>
+        <v>0.26648087860000003</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -18455,16 +18451,16 @@
         <v>54</v>
       </c>
       <c r="B4">
-        <v>0.03</v>
+        <v>6.12805108E-2</v>
       </c>
       <c r="C4">
-        <v>7.0000000000000007E-2</v>
+        <v>7.2743640999999998E-2</v>
       </c>
       <c r="D4">
-        <v>0.09</v>
+        <v>8.1762265200000003E-2</v>
       </c>
       <c r="E4">
-        <v>0.1</v>
+        <v>9.0501512400000012E-2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -18472,16 +18468,16 @@
         <v>51</v>
       </c>
       <c r="B5">
-        <v>0.05</v>
+        <v>6.2942702399999995E-2</v>
       </c>
       <c r="C5">
-        <v>0.08</v>
+        <v>7.6847298399999986E-2</v>
       </c>
       <c r="D5">
-        <v>0.09</v>
+        <v>8.8275958000000002E-2</v>
       </c>
       <c r="E5">
-        <v>0.1</v>
+        <v>0.1013269326</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -18489,16 +18485,16 @@
         <v>52</v>
       </c>
       <c r="B6">
-        <v>0.05</v>
+        <v>5.51861342E-2</v>
       </c>
       <c r="C6">
-        <v>7.0000000000000007E-2</v>
+        <v>6.6106687800000008E-2</v>
       </c>
       <c r="D6">
-        <v>0.08</v>
+        <v>7.7183961999999995E-2</v>
       </c>
       <c r="E6">
-        <v>0.09</v>
+        <v>9.18227026E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -18506,16 +18502,16 @@
         <v>53</v>
       </c>
       <c r="B7">
-        <v>0.04</v>
+        <v>5.3738795399999997E-2</v>
       </c>
       <c r="C7">
-        <v>0.06</v>
+        <v>6.7262267000000001E-2</v>
       </c>
       <c r="D7">
-        <v>0.08</v>
+        <v>7.78278788E-2</v>
       </c>
       <c r="E7">
-        <v>0.1</v>
+        <v>8.8054319399999997E-2</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -18523,16 +18519,16 @@
         <v>38</v>
       </c>
       <c r="B8">
-        <v>1.5</v>
+        <v>2.4546965014</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>3.025574013</v>
       </c>
       <c r="D8">
-        <v>3.5</v>
+        <v>3.2429962722000001</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3.4173586820000001</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -18540,16 +18536,16 @@
         <v>48</v>
       </c>
       <c r="B9">
-        <v>1.5</v>
+        <v>2.3798941623999998</v>
       </c>
       <c r="C9">
-        <v>2.5</v>
+        <v>2.7838294289999999</v>
       </c>
       <c r="D9">
-        <v>3.5</v>
+        <v>3.2512240889999999</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3.5884753159999998</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -18557,16 +18553,16 @@
         <v>39</v>
       </c>
       <c r="B10">
-        <v>1.5</v>
+        <v>2.7513101078000002</v>
       </c>
       <c r="C10">
-        <v>2.5</v>
+        <v>3.0273816949999999</v>
       </c>
       <c r="D10">
-        <v>3.5</v>
+        <v>3.1501577286</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3.3289630479999999</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -18574,16 +18570,16 @@
         <v>40</v>
       </c>
       <c r="B11">
-        <v>1.5</v>
+        <v>2.7940100002000001</v>
       </c>
       <c r="C11">
-        <v>2.5</v>
+        <v>2.9692380973999999</v>
       </c>
       <c r="D11">
-        <v>3.5</v>
+        <v>3.0955565479999998</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3.2967260301999999</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -18591,16 +18587,16 @@
         <v>41</v>
       </c>
       <c r="B12">
-        <v>1.5</v>
+        <v>3.5128583976000001</v>
       </c>
       <c r="C12">
-        <v>2.5</v>
+        <v>3.6731571465999999</v>
       </c>
       <c r="D12">
-        <v>3.5</v>
+        <v>3.7726051256000002</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>3.8635565789999999</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -18608,16 +18604,16 @@
         <v>49</v>
       </c>
       <c r="B13">
-        <v>1.5</v>
+        <v>2.4436313157999998</v>
       </c>
       <c r="C13">
-        <v>2.5</v>
+        <v>2.8307023184000002</v>
       </c>
       <c r="D13">
-        <v>3.5</v>
+        <v>3.4136013204000002</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3.7594713114</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -18625,16 +18621,16 @@
         <v>42</v>
       </c>
       <c r="B14">
-        <v>1.5</v>
+        <v>2.1328066718000001</v>
       </c>
       <c r="C14">
-        <v>2.5</v>
+        <v>2.3497129412</v>
       </c>
       <c r="D14">
-        <v>3.5</v>
+        <v>2.6946041988</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>2.9755396946000001</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -18642,16 +18638,16 @@
         <v>43</v>
       </c>
       <c r="B15">
-        <v>20</v>
+        <v>19.523724319999999</v>
       </c>
       <c r="C15">
-        <v>35</v>
+        <v>31.232038876000001</v>
       </c>
       <c r="D15">
-        <v>55</v>
+        <v>44.046977265999999</v>
       </c>
       <c r="E15">
-        <v>70</v>
+        <v>59.668771935999999</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -18659,16 +18655,16 @@
         <v>44</v>
       </c>
       <c r="B16">
-        <v>25</v>
+        <v>33.979886182000008</v>
       </c>
       <c r="C16">
-        <v>45</v>
+        <v>46.191276428000023</v>
       </c>
       <c r="D16">
-        <v>60</v>
+        <v>58.17058376</v>
       </c>
       <c r="E16">
-        <v>75</v>
+        <v>71.317825716000002</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -18676,16 +18672,16 @@
         <v>45</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>0.87516348420000056</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>4.2128407086000008</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>12.23476695800001</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -18693,16 +18689,16 @@
         <v>13</v>
       </c>
       <c r="B18">
-        <v>0.05</v>
+        <v>0.27690251500000002</v>
       </c>
       <c r="C18">
-        <v>0.15</v>
+        <v>0.3240145888</v>
       </c>
       <c r="D18">
-        <v>0.25</v>
+        <v>0.37230828119999998</v>
       </c>
       <c r="E18">
-        <v>0.45</v>
+        <v>0.44905015139999999</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -18710,16 +18706,16 @@
         <v>46</v>
       </c>
       <c r="B19">
-        <v>0.1</v>
+        <v>0.1127206516</v>
       </c>
       <c r="C19">
-        <v>0.2</v>
+        <v>0.18460571819999999</v>
       </c>
       <c r="D19">
-        <v>0.3</v>
+        <v>0.27134703760000001</v>
       </c>
       <c r="E19">
-        <v>0.4</v>
+        <v>0.32734106619999997</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -18727,16 +18723,16 @@
         <v>47</v>
       </c>
       <c r="B20">
-        <v>0.3</v>
+        <v>0.36849241700000002</v>
       </c>
       <c r="C20">
-        <v>0.4</v>
+        <v>0.40041762819999999</v>
       </c>
       <c r="D20">
-        <v>0.5</v>
+        <v>0.42545152879999998</v>
       </c>
       <c r="E20">
-        <v>0.6</v>
+        <v>0.46673236359999998</v>
       </c>
     </row>
   </sheetData>

--- a/appdata/threshold_definitions_res_hist_de.xlsx
+++ b/appdata/threshold_definitions_res_hist_de.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zhaw-my.sharepoint.com/personal/hedd_zhaw_ch/Documents/Dashboard Squarefoot Projekt/Squarefoot/Squarefoot code/squarefoot/appdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:9_{36C0AF89-E858-44E3-B955-074CA1A8DB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{302DD912-46E4-462A-82DE-37BD3004E8FF}"/>
+  <xr:revisionPtr revIDLastSave="242" documentId="13_ncr:9_{36C0AF89-E858-44E3-B955-074CA1A8DB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{959687E3-0A60-4DA5-8D3B-7A82C3303197}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="1770" windowWidth="21600" windowHeight="11295" xr2:uid="{DF7BF7E8-8078-438A-9C9E-DC555A1DD317}"/>
+    <workbookView xWindow="9105" yWindow="2670" windowWidth="21600" windowHeight="11295" xr2:uid="{DF7BF7E8-8078-438A-9C9E-DC555A1DD317}"/>
   </bookViews>
   <sheets>
     <sheet name="Schwellenwerte" sheetId="3" r:id="rId1"/>
@@ -44,15 +44,6 @@
     <t>anzahl_arten</t>
   </si>
   <si>
-    <t>temperatur</t>
-  </si>
-  <si>
-    <t>reaktion</t>
-  </si>
-  <si>
-    <t>feuchtigkeit</t>
-  </si>
-  <si>
     <t>licht</t>
   </si>
   <si>
@@ -74,9 +65,6 @@
     <t>konkurrenzstrategie</t>
   </si>
   <si>
-    <t>na0ehrstoff</t>
-  </si>
-  <si>
     <t>mahdvertra0eglichkeit</t>
   </si>
   <si>
@@ -105,6 +93,18 @@
   </si>
   <si>
     <t>gross</t>
+  </si>
+  <si>
+    <t>temperaturzahl</t>
+  </si>
+  <si>
+    <t>na0ehrstoffzahl</t>
+  </si>
+  <si>
+    <t>reaktionszahl</t>
+  </si>
+  <si>
+    <t>feuchtigkeitszahl</t>
   </si>
 </sst>
 </file>
@@ -637,10 +637,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -971,16 +967,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -1002,7 +998,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>0.1727265258</v>
@@ -1019,7 +1015,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>6.12805108E-2</v>
@@ -1036,7 +1032,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>6.2942702399999995E-2</v>
@@ -1053,7 +1049,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>5.51861342E-2</v>
@@ -1070,7 +1066,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>5.3738795399999997E-2</v>
@@ -1087,7 +1083,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>2.4546965014</v>
@@ -1104,7 +1100,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>2.3798941623999998</v>
@@ -1121,7 +1117,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>2.7513101078000002</v>
@@ -1138,7 +1134,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>2.7940100002000001</v>
@@ -1155,7 +1151,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B12">
         <v>3.5128583976000001</v>
@@ -1172,7 +1168,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>2.4436313157999998</v>
@@ -1189,7 +1185,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B14">
         <v>2.1328066718000001</v>
@@ -1206,7 +1202,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B15">
         <v>19.523724319999999</v>
@@ -1223,7 +1219,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16">
         <v>33.979886182000008</v>
@@ -1240,7 +1236,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1274,7 +1270,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>0.1127206516</v>
@@ -1291,7 +1287,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B20">
         <v>0.36849241700000002</v>
